--- a/artfynd/A 48790-2021 artfynd.xlsx
+++ b/artfynd/A 48790-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48790-2021 artfynd.xlsx
+++ b/artfynd/A 48790-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>67504130</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603660.1641799754</v>
+        <v>603660</v>
       </c>
       <c r="R2" t="n">
-        <v>6563035.554828621</v>
+        <v>6563036</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2017-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98130589</v>
+        <v>98130715</v>
       </c>
       <c r="B3" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +796,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221223</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hökkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603618.9272111361</v>
+        <v>603619</v>
       </c>
       <c r="R3" t="n">
-        <v>6563116.952914126</v>
+        <v>6563117</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +857,9 @@
           <t>1978-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98130556</v>
+        <v>111858827</v>
       </c>
       <c r="B4" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,16 +902,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220320</v>
+        <v>245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,20 +919,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hökkärr, Srm</t>
+          <t>Näverkärr 600m OSO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603618.9272111361</v>
+        <v>603535</v>
       </c>
       <c r="R4" t="n">
-        <v>6563116.952914126</v>
+        <v>6563030</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,55 +982,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sydvänd bergsida med moränbrant</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98130623</v>
+        <v>98130556</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>220320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603618.9272111361</v>
+        <v>603619</v>
       </c>
       <c r="R5" t="n">
-        <v>6563116.952914126</v>
+        <v>6563117</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,19 +1074,9 @@
           <t>1978-09-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,32 +1108,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98130715</v>
+        <v>111858836</v>
       </c>
       <c r="B6" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,24 +1136,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hökkärr, Srm</t>
+          <t>Näverkärr 600m OSO, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603618.9272111361</v>
+        <v>603535</v>
       </c>
       <c r="R6" t="n">
-        <v>6563116.952914126</v>
+        <v>6563030</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1978-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,26 +1191,231 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>sydvänd bergsida med moränbrant</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98130589</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hökkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603619</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6563117</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1978-09-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1978-09-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sydvänd bergsida med moränbrant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98130623</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hökkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603619</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6563117</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1978-09-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1978-09-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>sydvänd bergsida med moränbrant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48790-2021 artfynd.xlsx
+++ b/artfynd/A 48790-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67504130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98130715</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858827</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98130556</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858836</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98130589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,8 +1451,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98130623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>